--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487930_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487930_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.852</v>
+        <v>2.961</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5487</v>
+        <v>3.3641</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6967</v>
+        <v>-0.4031</v>
       </c>
       <c r="G2" t="n">
         <v>1.9208</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8607</v>
+        <v>-0.7517</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8358</v>
+        <v>-0.0204</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0249</v>
+        <v>-0.7313</v>
       </c>
       <c r="V2" t="n">
         <v>1.1675</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3286</v>
+        <v>0.5813</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4832</v>
+        <v>-0.9957</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8119</v>
+        <v>1.577</v>
       </c>
       <c r="G3" t="n">
         <v>-1.7266</v>
@@ -688,13 +688,13 @@
         <v>3.7461</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7659</v>
+        <v>0.0186</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0588</v>
+        <v>0.5463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2929</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5474</v>
+        <v>0.0247</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4456</v>
+        <v>0.0403</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1018</v>
+        <v>-0.0156</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3867</v>
@@ -766,13 +766,13 @@
         <v>2.4974</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3503</v>
+        <v>-0.1724</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6706</v>
+        <v>0.2653</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3203</v>
+        <v>-0.4377</v>
       </c>
       <c r="V4" t="n">
         <v>0.5838</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>L. DE LA FUENTE REDRUELLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4356</v>
+        <v>-0.4652</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6449</v>
+        <v>-0.1305</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2093</v>
+        <v>-0.3348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5904</v>
+        <v>-0.049</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1897</v>
+        <v>-0.049</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5993000000000001</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0104</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3504</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0696</v>
+        <v>-0.049</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8207</v>
+        <v>-0.049</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7511</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4828</v>
+        <v>-0.4162</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0562</v>
+        <v>-0.1305</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4266</v>
+        <v>-0.2857</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. DE LA FUENTE REDRUELLO</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4652</v>
+        <v>-0.5259</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1305</v>
+        <v>-0.794</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3348</v>
+        <v>0.268</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.049</v>
+        <v>0.5904</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.049</v>
+        <v>1.1897</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.0104</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.3504</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.049</v>
+        <v>-0.0696</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.049</v>
+        <v>-0.8207</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.7511</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4162</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1305</v>
+        <v>-0.2052</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2857</v>
+        <v>-0.3679</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9369</v>
+        <v>-1.6345</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.127</v>
+        <v>-0.9127</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8099</v>
+        <v>-0.7218</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7686</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5409</v>
+        <v>-0.2385</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3138</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.227</v>
+        <v>-0.139</v>
       </c>
       <c r="V7" t="n">
         <v>0.1238</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.519</v>
+        <v>-2.0302</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3967</v>
+        <v>-2.2896</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1223</v>
+        <v>0.2594</v>
       </c>
       <c r="G8" t="n">
         <v>0.2117</v>
@@ -1078,13 +1078,13 @@
         <v>2.7055</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2957</v>
+        <v>-0.8069</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1214</v>
+        <v>-0.0142</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1743</v>
+        <v>-0.7926</v>
       </c>
       <c r="V8" t="n">
         <v>0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5704</v>
+        <v>-2.2359</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5489</v>
+        <v>-2.0969</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0216</v>
+        <v>-0.139</v>
       </c>
       <c r="G9" t="n">
         <v>0.5983000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>3.3299</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5475</v>
+        <v>-1.213</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6186</v>
+        <v>-0.1666</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-1.0464</v>
       </c>
       <c r="V9" t="n">
         <v>0.4599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8858</v>
+        <v>-3.4627</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0389</v>
+        <v>-2.1461</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8468</v>
+        <v>-1.3166</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6791</v>
@@ -1234,13 +1234,13 @@
         <v>2.4974</v>
       </c>
       <c r="S10" t="n">
-        <v>0.274</v>
+        <v>-0.3029</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.109</v>
+        <v>-0.2162</v>
       </c>
       <c r="U10" t="n">
-        <v>0.383</v>
+        <v>-0.0867</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9376</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.266299999999999</v>
+        <v>-7.9112</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.2081</v>
+        <v>-7.9704</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0583</v>
+        <v>0.0592</v>
       </c>
       <c r="G11" t="n">
         <v>-6.2847</v>
@@ -1312,13 +1312,13 @@
         <v>2.9137</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6924</v>
+        <v>-1.3373</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.37</v>
+        <v>-0.1323</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3224</v>
+        <v>-1.2049</v>
       </c>
       <c r="V11" t="n">
         <v>1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.3512</v>
+        <v>-14.6986</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.5839</v>
+        <v>-13.9315</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7673999999999994</v>
+        <v>-0.7673</v>
       </c>
       <c r="G12" t="n">
         <v>-11.5735</v>
@@ -1390,13 +1390,13 @@
         <v>22.893</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.446000000000001</v>
+        <v>-5.7934</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8259</v>
+        <v>-0.1732999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.62</v>
+        <v>-5.619899999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.6274</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9165</v>
+        <v>5.011</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5311</v>
+        <v>2.424</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3854</v>
+        <v>2.587</v>
       </c>
       <c r="G13" t="n">
         <v>2.1102</v>
@@ -1468,13 +1468,13 @@
         <v>2.9137</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8064</v>
+        <v>0.9008</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7887</v>
+        <v>0.6815</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0177</v>
+        <v>0.2193</v>
       </c>
       <c r="V13" t="n">
         <v>1.1675</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3003</v>
+        <v>4.6462</v>
       </c>
       <c r="E14" t="n">
-        <v>3.371</v>
+        <v>3.0496</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9292</v>
+        <v>1.5967</v>
       </c>
       <c r="G14" t="n">
         <v>3.1384</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0588</v>
+        <v>1.4048</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4907</v>
+        <v>1.1692</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4318</v>
+        <v>0.2356</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9376</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0464</v>
+        <v>3.7759</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0584</v>
+        <v>3.7369</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0119</v>
+        <v>0.039</v>
       </c>
       <c r="G15" t="n">
         <v>2.1989</v>
@@ -1624,13 +1624,13 @@
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3283</v>
+        <v>1.0577</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.5853</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4215</v>
+        <v>0.4724</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9376</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5446</v>
+        <v>2.183</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9829</v>
+        <v>1.6717</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5617</v>
+        <v>0.5112</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5926</v>
+        <v>2.1104</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3281</v>
+        <v>-0.3838</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2645</v>
+        <v>2.4942</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1766</v>
+        <v>2.3351</v>
       </c>
       <c r="K16" t="n">
-        <v>4.0591</v>
+        <v>-0.0856</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1176</v>
+        <v>2.4207</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.584</v>
+        <v>-0.2247</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.731</v>
+        <v>-0.2982</v>
       </c>
       <c r="O16" t="n">
-        <v>0.147</v>
+        <v>0.0735</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.7055</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.2029</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4974</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8874</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4254</v>
+        <v>0.3772</v>
       </c>
       <c r="U16" t="n">
-        <v>0.462</v>
+        <v>0.2604</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8137</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.021</v>
+        <v>2.0597</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5646</v>
+        <v>0.4471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4564</v>
+        <v>1.6126</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1104</v>
+        <v>3.5926</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3838</v>
+        <v>3.3281</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4942</v>
+        <v>0.2645</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3351</v>
+        <v>4.1766</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0856</v>
+        <v>4.0591</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4207</v>
+        <v>0.1176</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2247</v>
+        <v>-0.584</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2982</v>
+        <v>-0.731</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0735</v>
+        <v>0.147</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8325</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-5.2029</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>2.4974</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4756</v>
+        <v>1.4025</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2701</v>
+        <v>0.8897</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2056</v>
+        <v>0.5129</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3975</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2891</v>
+        <v>0.9141</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.292</v>
+        <v>-1.0342</v>
       </c>
       <c r="F18" t="n">
-        <v>0.581</v>
+        <v>1.9483</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1687</v>
+        <v>-0.1858</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7036</v>
+        <v>-0.3539</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5349</v>
+        <v>0.1682</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0871</v>
+        <v>-0.1529</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5159</v>
+        <v>-0.1048</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4287</v>
+        <v>-0.0482</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08160000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1877</v>
+        <v>-0.2492</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1061</v>
+        <v>0.2164</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5585</v>
+        <v>0.1623</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6615</v>
+        <v>0.0324</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1031</v>
+        <v>0.1299</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.23</v>
+        <v>0.9376</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.234</v>
+        <v>0.85</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9067</v>
+        <v>-1.3709</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1407</v>
+        <v>2.2209</v>
       </c>
       <c r="G19" t="n">
         <v>2.977</v>
@@ -1936,13 +1936,13 @@
         <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6087</v>
+        <v>1.2248</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1272</v>
+        <v>0.663</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4816</v>
+        <v>0.5618</v>
       </c>
       <c r="V19" t="n">
         <v>-0.23</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.2509</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7843</v>
+        <v>-0.5063</v>
       </c>
       <c r="F20" t="n">
-        <v>1.776</v>
+        <v>0.7572</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1858</v>
+        <v>0.1687</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3539</v>
+        <v>1.7036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1682</v>
+        <v>-1.5349</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1529</v>
+        <v>0.0871</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1048</v>
+        <v>1.5159</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0482</v>
+        <v>-1.4287</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0328</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2492</v>
+        <v>0.1877</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2164</v>
+        <v>-0.1061</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.76</v>
+        <v>0.5203</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>0.4472</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0424</v>
+        <v>0.0731</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9376</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-0.23</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.022</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2171</v>
+        <v>-2.1467</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1423</v>
+        <v>2.1247</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3988</v>
+        <v>-3.1314</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0298</v>
+        <v>-0.4372</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4286</v>
+        <v>-2.6942</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0192</v>
+        <v>-2.5597</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0192</v>
+        <v>0.1019</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-2.6616</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3796</v>
+        <v>-0.5717</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.049</v>
+        <v>-0.5391</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4286</v>
+        <v>-0.0326</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2081</v>
+        <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3588</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1957</v>
+        <v>0.4129</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5546</v>
+        <v>0.4071</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5153</v>
+        <v>-0.1145</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9229</v>
+        <v>-1.11</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4076</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5545</v>
+        <v>0.3988</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0574</v>
+        <v>-0.0298</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5029</v>
+        <v>0.4286</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2359</v>
+        <v>0.0192</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5225</v>
+        <v>0.0192</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2865</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3186</v>
+        <v>0.3796</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5349</v>
+        <v>-0.049</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2164</v>
+        <v>0.4286</v>
       </c>
       <c r="P22" t="n">
         <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0659</v>
+        <v>0.3192</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2048</v>
+        <v>-0.0886</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2707</v>
+        <v>0.4078</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9376</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.165</v>
+        <v>-0.3035</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.004</v>
+        <v>-3.0301</v>
       </c>
       <c r="F23" t="n">
-        <v>1.839</v>
+        <v>2.7266</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1314</v>
+        <v>-0.5545</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4372</v>
+        <v>-1.0574</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6942</v>
+        <v>0.5029</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5597</v>
+        <v>-0.2359</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1019</v>
+        <v>-0.5225</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6616</v>
+        <v>0.2865</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5717</v>
+        <v>-0.3186</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5391</v>
+        <v>-0.5349</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0326</v>
+        <v>0.2164</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2893</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R23" t="n">
         <v>2.2893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3229</v>
+        <v>0.146</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4443</v>
+        <v>0.0977</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1214</v>
+        <v>0.0483</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.9376</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2373</v>
+        <v>-1.7565</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6137</v>
+        <v>-1.3638</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6237</v>
+        <v>-0.3927</v>
       </c>
       <c r="G24" t="n">
         <v>-1.25</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5121</v>
+        <v>-0.007</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1025</v>
+        <v>0.3524</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5904</v>
+        <v>-0.3595</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7076</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.3513</v>
+        <v>17.4943</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7672999999999998</v>
+        <v>0.7672999999999992</v>
       </c>
       <c r="F25" t="n">
-        <v>14.5837</v>
+        <v>16.727</v>
       </c>
       <c r="G25" t="n">
         <v>11.5733</v>
       </c>
       <c r="H25" t="n">
-        <v>6.225700000000002</v>
+        <v>6.225700000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>5.347399999999999</v>
+        <v>5.3474</v>
       </c>
       <c r="J25" t="n">
         <v>15.6168</v>
@@ -2383,7 +2383,7 @@
         <v>11.3716</v>
       </c>
       <c r="L25" t="n">
-        <v>4.2453</v>
+        <v>4.245299999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-4.0435</v>
@@ -2404,13 +2404,13 @@
         <v>21.8525</v>
       </c>
       <c r="S25" t="n">
-        <v>6.4458</v>
+        <v>8.589100000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>5.619999999999999</v>
+        <v>5.6199</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8259999999999998</v>
+        <v>2.969099999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6276</v>
@@ -2419,7 +2419,7 @@
         <v>2.4236</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.050999999999999</v>
+        <v>-4.051</v>
       </c>
     </row>
   </sheetData>
